--- a/outputs/Block5B_Senate_Specification_Summary.xlsx
+++ b/outputs/Block5B_Senate_Specification_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Specification</t>
   </si>
@@ -31,40 +31,28 @@
     <t>Uses State Effects</t>
   </si>
   <si>
+    <t>PooledPollStructure</t>
+  </si>
+  <si>
+    <t>PooledFullV11</t>
+  </si>
+  <si>
     <t>NestedSpecificationSelector</t>
   </si>
   <si>
-    <t>PooledFullV11</t>
-  </si>
-  <si>
-    <t>PooledNationalReduced</t>
-  </si>
-  <si>
-    <t>PooledPollStructure</t>
-  </si>
-  <si>
     <t>PartialPoolFull</t>
   </si>
   <si>
-    <t>PooledPopularContext</t>
+    <t>Race-level poll structure and incumbent party only</t>
+  </si>
+  <si>
+    <t>Production pooled state-error model: race-level poll structure + frozen national popular-vote context; no legacy bucket signals</t>
   </si>
   <si>
     <t>Specification, alpha and correction size selected inside each outer fold</t>
   </si>
   <si>
-    <t>Exact pooled production specification inherited from v12</t>
-  </si>
-  <si>
-    <t>Adds non-quota national Senate context</t>
-  </si>
-  <si>
-    <t>Poll structure and incumbency only</t>
-  </si>
-  <si>
-    <t>Regularized state effects; safer alternative to 11 tiny models</t>
-  </si>
-  <si>
-    <t>Adds frozen national popular-vote context</t>
+    <t>Clean-feature challenger with regularized state effects</t>
   </si>
   <si>
     <t>Selected only if validated</t>
@@ -425,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -450,16 +438,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>5.115767368378489</v>
+        <v>5.357505220532191</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
-        <v>17</v>
+      <c r="E2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -467,13 +455,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>5.116327771031301</v>
+        <v>5.392670902908676</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -484,16 +472,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>5.415582115715334</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4">
-        <v>5.27556650673071</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -501,50 +489,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>5.357505220532191</v>
+        <v>5.711037019968246</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>5.369068690363362</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>5.392670902908676</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
